--- a/src/attributions/attributions_ig_traj_80.xlsx
+++ b/src/attributions/attributions_ig_traj_80.xlsx
@@ -999,7 +999,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02394092632924144</v>
+        <v>0.1357213956063731</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04737869069218277</v>
+        <v>-0.1106192160997437</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0687263685828748</v>
+        <v>0.02820293347749772</v>
       </c>
       <c r="F2" t="n">
         <v>-0</v>
@@ -1020,25 +1020,25 @@
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07200801432171179</v>
+        <v>0.1607406908904881</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01396478623361789</v>
+        <v>-0.3013537236583012</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.06907899306029104</v>
+        <v>0.02095735111112306</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -1047,13 +1047,13 @@
         <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02592058921947108</v>
+        <v>0.02009401622149363</v>
       </c>
       <c r="T2" t="n">
         <v>-0</v>
@@ -1062,91 +1062,91 @@
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09340842381038526</v>
+        <v>-0.0758097820188612</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03130339279830054</v>
+        <v>0.08607788860958358</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.002851801335650072</v>
+        <v>0.006508000331449859</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.0344727708704435</v>
+        <v>0.1083243131726383</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01411038664133246</v>
+        <v>0.1697078403188617</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02309732901816538</v>
+        <v>0.008308698419650259</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.01486262558060095</v>
+        <v>-0.01731745942932602</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06283453873230342</v>
+        <v>0.07034262381493707</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.01438911099255462</v>
+        <v>-0.005436418898391149</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.02276828455198836</v>
+        <v>-0.08726165991515752</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.01183823534383922</v>
+        <v>-0.003394222106815319</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
@@ -1158,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.03155251487596699</v>
+        <v>0.1383048577042964</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -1170,52 +1170,52 @@
         <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.002581439954956081</v>
+        <v>0.1198478749963248</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.02235394201285093</v>
+        <v>0.06849395437896214</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.03087649112700357</v>
+        <v>-0.005934929285718425</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01162501093338994</v>
+        <v>0.1752628701884147</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.008739102550135084</v>
+        <v>-0.3280892418448545</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.01026856340313644</v>
+        <v>-0.09079654856697777</v>
       </c>
       <c r="BV2" t="n">
         <v>-0</v>
@@ -1224,37 +1224,37 @@
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0007358185974277789</v>
+        <v>-0.2886754595779423</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.04082188383782141</v>
+        <v>-0.08207911050247929</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.01118785406560184</v>
+        <v>-0.09145888243047133</v>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.007797836553935383</v>
+        <v>0.1681203506112005</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.02072217619577005</v>
+        <v>-0.04271722343307918</v>
       </c>
       <c r="CI2" t="n">
         <v>0</v>
@@ -1263,52 +1263,52 @@
         <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.0037524436061281</v>
+        <v>0.04987833947563877</v>
       </c>
       <c r="CN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.0250987332193468</v>
+        <v>0.3091568844597778</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.04909057745741415</v>
+        <v>-0.006274791296799758</v>
       </c>
       <c r="CR2" t="n">
         <v>0</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.006133870860311784</v>
+        <v>-0.1017536813316136</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="n">
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.01491518537000321</v>
+        <v>0.1623728457594358</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.03547509364258496</v>
+        <v>-0.02037728656632841</v>
       </c>
       <c r="DA2" t="n">
         <v>-0</v>
@@ -1317,25 +1317,25 @@
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
         <v>-0</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.002217122834552273</v>
+        <v>0.0013322761937011</v>
       </c>
       <c r="DF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.06416965779138531</v>
+        <v>0.05307424339356037</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.05585497434061494</v>
+        <v>-0.02752388931481558</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
@@ -1347,28 +1347,28 @@
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.002884060647310469</v>
+        <v>0.03860033402142082</v>
       </c>
       <c r="DO2" t="n">
         <v>-0</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.01895263501235869</v>
+        <v>0.1355538444953028</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.1034217657051097</v>
+        <v>-0.08234489891575499</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
         <v>-0</v>
@@ -1377,25 +1377,25 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.00729196034322644</v>
+        <v>-0.02529981432666994</v>
       </c>
       <c r="DX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.008249161542692014</v>
+        <v>-0.07854461808255751</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.03280690868587788</v>
+        <v>-0.09227726029547108</v>
       </c>
       <c r="EB2" t="n">
         <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
@@ -1404,73 +1404,73 @@
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.01677180019557874</v>
+        <v>-0.1798887576668088</v>
       </c>
       <c r="EG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.03565718356415532</v>
+        <v>0.1682508603596288</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.08419176871232947</v>
+        <v>-0.02914008496493016</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0.02802871556604173</v>
+        <v>0.06512375370601153</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.006275292382618154</v>
+        <v>0.2686698094439307</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.05217510566426688</v>
+        <v>-0.09050843566575578</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0.008837534930016837</v>
+        <v>-0.09740019854120854</v>
       </c>
       <c r="EY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ2" t="n">
         <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.007528061814176132</v>
+        <v>0.1995720864429351</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.03430455635138342</v>
+        <v>0.006752678048645773</v>
       </c>
       <c r="FC2" t="n">
         <v>0</v>
@@ -1479,67 +1479,67 @@
         <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.01735606272529178</v>
+        <v>-0.07475584641857541</v>
       </c>
       <c r="FH2" t="n">
         <v>0</v>
       </c>
       <c r="FI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.05155398105349183</v>
+        <v>0.2307675515281181</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.06938520987199787</v>
+        <v>0.02491288314647171</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0.0195193089742912</v>
+        <v>-0.09218677525747765</v>
       </c>
       <c r="FQ2" t="n">
         <v>0</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.03508992439640592</v>
+        <v>0.2238590589469402</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.1510505264966768</v>
+        <v>-0.3140896758745105</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
         <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0.003483313476346797</v>
+        <v>-0.09041994734373601</v>
       </c>
       <c r="FZ2" t="n">
         <v>0</v>
@@ -1548,13 +1548,13 @@
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.03446025714747364</v>
+        <v>0.2076925364285798</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -1577,13 +1577,13 @@
         <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0630659001931053</v>
+        <v>-0.0157023444225848</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01300764756401055</v>
+        <v>0.005365576189993939</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5240954286294019</v>
+        <v>0.2007400808500759</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1604,16 +1604,16 @@
         <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05405252220731481</v>
+        <v>-0.05808871432184326</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.05525720831395486</v>
+        <v>-0.009274544968261684</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3895578008224662</v>
+        <v>0.2309078065760868</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1625,19 +1625,19 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01643674394651077</v>
+        <v>-0.03152031788940518</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06939873613788489</v>
+        <v>0.01255048115833722</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04519975493257287</v>
+        <v>0.01777793098534136</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>-0</v>
@@ -1655,19 +1655,19 @@
         <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.0539946543198986</v>
+        <v>0.05173685919634499</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.000731475144162448</v>
+        <v>0.02334977395649456</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03855298895738098</v>
+        <v>0.06033558722854047</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1676,22 +1676,22 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.03828147137014404</v>
+        <v>-0.04674486315815641</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.08486099760458013</v>
+        <v>-0.02706926493663437</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.05670348389126057</v>
+        <v>0.0341537400068978</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0</v>
@@ -1700,37 +1700,37 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0313681254931311</v>
+        <v>-0.01543169599139783</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.04310579127287367</v>
+        <v>-0.04578971234640274</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.3325697888168643</v>
+        <v>0.165817636723374</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
         <v>-0</v>
@@ -1739,13 +1739,13 @@
         <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.01209553597845399</v>
+        <v>0.03450882214548662</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.009287378463346888</v>
+        <v>0.01645522331436888</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.07097712646542201</v>
+        <v>-0.02870043489099646</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
@@ -1766,40 +1766,40 @@
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.02733952297264467</v>
+        <v>-0.05867286635435055</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.00559636509108988</v>
+        <v>-0.02413262877750774</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.03514048739457296</v>
+        <v>-0.0106989644583824</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0401298438780733</v>
+        <v>-0.1090409157906527</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.07580772388942704</v>
+        <v>-0.02875012996258803</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1560123355299239</v>
+        <v>0.08747946632581807</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
@@ -1808,52 +1808,52 @@
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.02159828231322356</v>
+        <v>0.001518374489106606</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.00867571310732208</v>
+        <v>0.03217191269398915</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.1023849726231967</v>
+        <v>-0.04910823544289269</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.03771215862096453</v>
+        <v>0.03777792050333731</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.09500487350482544</v>
+        <v>0.06866983753027332</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.009261628607069274</v>
+        <v>0.006801889142360472</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
@@ -1865,79 +1865,79 @@
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
         <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.02644305643145452</v>
+        <v>0.004099331126269624</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01555079161548294</v>
+        <v>0.009570589699384837</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.09727711389827733</v>
+        <v>-0.04773981144170204</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF3" t="n">
         <v>-0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.03258621407065847</v>
+        <v>0.008139049137376684</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.013928588507449</v>
+        <v>0.004963843055036864</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.03128692613813622</v>
+        <v>-0.03157349824278867</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.04395409460582739</v>
+        <v>-0.03426046263498658</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.04710913878632132</v>
+        <v>0.02827709159311167</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.01580127312378971</v>
+        <v>-0.03328586107515207</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,55 +1946,55 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0.007316915824470367</v>
+        <v>0.09502743926997874</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.007557786809462135</v>
+        <v>-0.01619934665813097</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.06475067601211205</v>
+        <v>0.008542569662113312</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.085015046155024</v>
+        <v>-0.00432817642817214</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01319452892834481</v>
+        <v>0.01102943031417475</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0900866339165938</v>
+        <v>0.0001182934639352795</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
@@ -2003,52 +2003,52 @@
         <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.05886629268000991</v>
+        <v>0.04412675944988342</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.04944761632630492</v>
+        <v>0.04666243881000518</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0718264947522245</v>
+        <v>-0.02038165248820437</v>
       </c>
       <c r="EU3" t="n">
         <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.0188312515658069</v>
+        <v>0.02088355994483684</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.004237364955702617</v>
+        <v>0.02960585477022736</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.09411699122155258</v>
+        <v>-0.0538545049080414</v>
       </c>
       <c r="FD3" t="n">
         <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
@@ -2057,31 +2057,31 @@
         <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0.005822987135418163</v>
+        <v>0.04130939207768868</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.03443632606135918</v>
+        <v>0.04158060906658458</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.02510756393004237</v>
+        <v>0.0605923402505487</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
         <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
         <v>0</v>
@@ -2090,46 +2090,46 @@
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0.01893127849923146</v>
+        <v>-0.02983928150785531</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.1561887957586328</v>
+        <v>-0.1252161337528357</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0.07997069028232594</v>
+        <v>0.008130722641396193</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.04949523247384263</v>
+        <v>0.06654930476979709</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.04010624219646641</v>
+        <v>0.01480824745665178</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>-0</v>
